--- a/erp-server/erp-server-plm/src/main/resources/excel/templateTaskExportTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/templateTaskExportTemplate.xlsx
@@ -17,6 +17,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -31,6 +38,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +59,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -59,6 +80,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -76,6 +104,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -114,11 +149,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -765,17 +801,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1126,8 +1171,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="8" width="14.4583333333333" customWidth="1"/>
     <col min="9" max="9" width="21.1833333333333" customWidth="1"/>
@@ -1135,45 +1180,50 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="12" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="12" spans="9:11">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
